--- a/experiments/overcast_experiments.xlsx
+++ b/experiments/overcast_experiments.xlsx
@@ -244,8 +244,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OvercastExperiments" displayName="OvercastExperiments" ref="A1:L7" totalsRowShown="0">
-  <autoFilter ref="A1:L7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OvercastExperiments" displayName="OvercastExperiments" ref="A1:L19" totalsRowShown="0">
+  <autoFilter ref="A1:L19">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -279,7 +279,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr defaultRowHeight="20" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -347,11 +347,15 @@
       <c r="F2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="4">
-        <v>4.7527</v>
-      </c>
-      <c r="H2" s="4">
-        <v>3.1924</v>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>4.8853</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>3.1814</t>
+        </is>
       </c>
       <c r="I2" s="4">
         <v>4.3256</v>
@@ -359,12 +363,14 @@
       <c r="J2" s="4">
         <v>2.5644</v>
       </c>
-      <c r="K2" s="4">
-        <v>-0.4271</v>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>-0.5597</t>
+        </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>-0.6280</t>
+          <t>-0.6170</t>
         </is>
       </c>
     </row>
@@ -387,11 +393,15 @@
       <c r="F3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>20</v>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>3.2097</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>1.5640</t>
+        </is>
       </c>
       <c r="I3" s="4">
         <v>4.9003</v>
@@ -401,12 +411,12 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>2.0819</t>
+          <t>1.6906</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.2249</t>
         </is>
       </c>
     </row>
@@ -429,11 +439,15 @@
       <c r="F4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="4">
-        <v>5.9813</v>
-      </c>
-      <c r="H4" s="4">
-        <v>3.3986</v>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>7.3659</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>4.0264</t>
+        </is>
       </c>
       <c r="I4" s="4">
         <v>7.6187</v>
@@ -441,11 +455,15 @@
       <c r="J4" s="4">
         <v>4.3014</v>
       </c>
-      <c r="K4" s="4">
-        <v>1.6374</v>
-      </c>
-      <c r="L4" s="4">
-        <v>0.9028</v>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>0.2528</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>0.2750</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -467,12 +485,14 @@
       <c r="F5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="4">
-        <v>3.3202</v>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>3.7995</t>
+        </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>1.7230</t>
+          <t>2.0832</t>
         </is>
       </c>
       <c r="I5" s="4">
@@ -483,12 +503,14 @@
           <t>2.0990</t>
         </is>
       </c>
-      <c r="K5" s="4">
-        <v>0.6774</v>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>0.1981</t>
+        </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>0.3760</t>
+          <t>0.0158</t>
         </is>
       </c>
     </row>
@@ -511,11 +533,15 @@
       <c r="F6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="4">
-        <v>51.5551</v>
-      </c>
-      <c r="H6" s="4">
-        <v>45.2953</v>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>52.6956</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>46.2473</t>
+        </is>
       </c>
       <c r="I6" s="4">
         <v>48.2464</v>
@@ -523,11 +549,15 @@
       <c r="J6" s="4">
         <v>39.4751</v>
       </c>
-      <c r="K6" s="4">
-        <v>-3.3087</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-5.8202</v>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>-4.4492</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>-6.7722</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -549,11 +579,15 @@
       <c r="F7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="4">
-        <v>47.9105</v>
-      </c>
-      <c r="H7" s="4">
-        <v>42.1218</v>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>40.8864</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>35.8765</t>
+        </is>
       </c>
       <c r="I7" s="4">
         <v>43.3933</v>
@@ -563,59 +597,711 @@
           <t>35.3350</t>
         </is>
       </c>
-      <c r="K7" s="4">
-        <v>-4.5172</v>
-      </c>
-      <c r="L7" s="4">
-        <v>-6.7868</v>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>2.5069</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>-0.5415</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>average(6)</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="s">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>group7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>6.0146</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>4.2088</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>5.1739</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>3.4002</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>-0.8407</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>-0.8086</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>group8</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>3.0342</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>1.6863</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>4.9615</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>2.5188</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>1.9273</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>0.8325</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>group9</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>6.6403</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>4.2644</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>7.9919</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>4.6805</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>1.3516</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>0.4161</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>group10</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>3.2225</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>2.0252</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>4.4076</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>2.3897</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>1.1851</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>0.3645</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>group11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>48.4671</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>42.6642</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>45.0072</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>38.2727</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>-3.4599</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>-4.3915</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>group12</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>40.0936</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>34.7927</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>36.5214</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>30.9706</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>-3.5722</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>-3.8221</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>group13</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>4.6598</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>3.4071</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>4.3971</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>2.6935</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>-0.2627</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>-0.7136</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>group14</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>3.1747</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>1.7128</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>4.3247</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>2.3042</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>1.1500</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>0.5914</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>group15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>6.7979</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>4.1955</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>6.6067</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>3.5566</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>-0.1912</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>-0.6389</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>group16</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>2.5897</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>1.4790</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>4.4571</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>2.6294</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>1.8674</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>1.1504</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>group17</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>51.1092</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>44.4759</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>46.5277</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>37.1637</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>-4.5815</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>-7.3122</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>group18</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>44.8566</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>38.6186</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>38.1554</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>31.1586</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>-6.7012</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>-7.4600</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>average(18)</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C20" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D20" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E20" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F20" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G20" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H20" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I20" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J20" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>-0.6427</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>-1.7729</t>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>-0.6938</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>-1.5671</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L7"/>
+  <autoFilter ref="A1:L19"/>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <tableParts count="1">
